--- a/49916_Cuenca_Aguaytia/_raw_reportes_xlsx/IDConfig_64905_completo.xlsx
+++ b/49916_Cuenca_Aguaytia/_raw_reportes_xlsx/IDConfig_64905_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R38586220636d441d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rb5384543f94a4879"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,1161 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    172.6242</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     91.0983</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    163.2995</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     82.3990</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     84.3035</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     80.3237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    107.3120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    124.0140</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.5884</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    372.7923</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    105.9375</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.6243</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    206.8877</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.9165</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    286.7016</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     84.1636</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    113.6415</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     75.2760</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     81.3055</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     99.2838</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.7348</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    115.9790</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    176.9282</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    554.8805</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     69.0730</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     61.7890</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     56.0577</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     61.6460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     64.9520</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.2683</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    185.0305</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     71.3110</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     62.4866</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     53.1445</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     82.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     56.2352</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.5660</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     66.7919</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.7995</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     77.4925</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.5983</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     69.4671</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    101.6658</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    189.1232</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     56.8391</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     47.5978</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    103.4937</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     76.8779</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     46.9347</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     39.2294</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     41.4203</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     47.9542</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     52.1573</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     61.7644</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     97.6228</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    114.5453</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     85.9054</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     79.0998</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     84.2604</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     90.4837</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     94.5656</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     92.1716</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    106.6758</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    233.5961</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     94.5159</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     99.5470</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.1044</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     99.8487</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    134.2291</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    142.4388</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.4834</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    229.8458</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    229.8458</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    255.5038</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    185.0358</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     85.6458</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>20/07/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +1419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.9976</x:v>
+        <x:v>     99.9994</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +1434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     25.4216</x:v>
+        <x:v>     95.7708</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +1449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.1389</x:v>
+        <x:v>    102.3504</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +1464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1272</x:v>
+        <x:v>     82.4434</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +1479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.1432</x:v>
+        <x:v>    126.4646</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +1494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.7144</x:v>
+        <x:v>    125.1666</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +1509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0040</x:v>
+        <x:v>    136.4550</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +1524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    107.7136</x:v>
+        <x:v>    228.8556</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +1539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    133.9404</x:v>
+        <x:v>    265.0243</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +1554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.1448</x:v>
+        <x:v>    129.9494</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +1569,22 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.4328</x:v>
+        <x:v>    137.5700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     81.9821</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +1599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.2824</x:v>
+        <x:v>     89.5529</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +1614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     21.9912</x:v>
+        <x:v>     83.7520</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -459,7 +1629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.2760</x:v>
+        <x:v>     97.8810</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -474,7 +1644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.2872</x:v>
+        <x:v>    129.6346</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +1659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.8616</x:v>
+        <x:v>    137.0334</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -504,7 +1674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.7192</x:v>
+        <x:v>    154.4388</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -519,7 +1689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.8408</x:v>
+        <x:v>     80.7985</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -534,7 +1704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.5565</x:v>
+        <x:v>     79.3957</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -549,7 +1719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.2760</x:v>
+        <x:v>     98.0693</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -564,7 +1734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.7080</x:v>
+        <x:v>    107.8971</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -579,7 +1749,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.5672</x:v>
+        <x:v>    112.6597</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -594,7 +1764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.1389</x:v>
+        <x:v>    129.5701</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -609,7 +1779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     73.4472</x:v>
+        <x:v>    161.0359</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -624,7 +1794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    149.2276</x:v>
+        <x:v>    297.5666</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -639,7 +1809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     61.4408</x:v>
+        <x:v>    162.1496</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -654,7 +1824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     56.2952</x:v>
+        <x:v>    152.7508</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -669,7 +1839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     16.8456</x:v>
+        <x:v>     92.8347</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -684,7 +1854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     21.9912</x:v>
+        <x:v>    100.0922</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -699,7 +1869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.2872</x:v>
+        <x:v>    131.9373</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -714,7 +1884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.5672</x:v>
+        <x:v>    113.9240</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -729,7 +1899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     17.4173</x:v>
+        <x:v>     88.1259</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -744,7 +1914,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.7176</x:v>
+        <x:v>    134.6057</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -759,7 +1929,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     19.7043</x:v>
+        <x:v>     88.7675</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -774,7 +1944,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.9960</x:v>
+        <x:v>    115.0174</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -789,7 +1959,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.4344</x:v>
+        <x:v>    141.7112</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -804,7 +1974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    101.6754</x:v>
+        <x:v>    224.1676</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -819,7 +1989,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     67.0152</x:v>
+        <x:v>    170.5113</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -834,7 +2004,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     23.2776</x:v>
+        <x:v>    102.4257</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -849,7 +2019,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.5704</x:v>
+        <x:v>    122.1310</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -864,7 +2034,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     92.3144</x:v>
+        <x:v>    218.6873</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -879,7 +2049,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     21.1336</x:v>
+        <x:v>     99.2825</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -894,7 +2064,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.8435</x:v>
+        <x:v>     81.5853</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -909,7 +2079,37 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.4232</x:v>
+        <x:v>    110.0921</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    126.3636</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    151.9129</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -924,7 +2124,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     15.1304</x:v>
+        <x:v>    133.3589</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -939,7 +2139,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.2792</x:v>
+        <x:v>     86.1138</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -954,7 +2154,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.5576</x:v>
+        <x:v>     74.6331</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -969,7 +2169,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     18.1320</x:v>
+        <x:v>     96.9651</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -984,7 +2184,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.0072</x:v>
+        <x:v>    150.1013</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -999,7 +2199,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.2760</x:v>
+        <x:v>     86.4057</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1014,7 +2214,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1256</x:v>
+        <x:v>     78.5443</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1029,7 +2229,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.8435</x:v>
+        <x:v>     81.5355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1044,7 +2244,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.7000</x:v>
+        <x:v>     69.5532</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1059,7 +2259,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     21.9912</x:v>
+        <x:v>    101.2112</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1074,7 +2274,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     24.9928</x:v>
+        <x:v>    104.1473</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1089,7 +2289,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     19.8472</x:v>
+        <x:v>     96.9382</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1104,7 +2304,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.1368</x:v>
+        <x:v>    107.3120</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1119,7 +2319,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.5752</x:v>
+        <x:v>    136.4429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1134,7 +2334,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.5800</x:v>
+        <x:v>    150.3568</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1149,7 +2349,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    102.4700</x:v>
+        <x:v>    237.5893</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1164,7 +2364,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     64.8712</x:v>
+        <x:v>    167.1690</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1179,7 +2379,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.5688</x:v>
+        <x:v>    116.6287</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1194,7 +2394,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     43.0024</x:v>
+        <x:v>    131.2109</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1209,7 +2409,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.1368</x:v>
+        <x:v>    107.3497</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1224,7 +2424,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.5720</x:v>
+        <x:v>    125.7503</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1239,7 +2439,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     57.5816</x:v>
+        <x:v>    154.6324</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1254,7 +2454,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    101.6824</x:v>
+        <x:v>    222.9252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1269,7 +2469,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    212.3986</x:v>
+        <x:v>    365.9172</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1284,7 +2484,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     76.7210</x:v>
+        <x:v>    195.0040</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1299,7 +2499,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     84.5960</x:v>
+        <x:v>    202.0928</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1314,7 +2514,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8632</x:v>
+        <x:v>    141.8416</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1329,7 +2529,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.2904</x:v>
+        <x:v>    138.4765</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1344,7 +2544,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.8648</x:v>
+        <x:v>    146.9835</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1359,7 +2559,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     53.7224</x:v>
+        <x:v>    148.1106</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1374,7 +2574,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    145.3194</x:v>
+        <x:v>    300.1601</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1389,7 +2589,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     64.8712</x:v>
+        <x:v>    167.0184</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1404,7 +2604,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     58.4392</x:v>
+        <x:v>    156.1361</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1419,7 +2619,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.8616</x:v>
+        <x:v>    137.0603</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1434,7 +2634,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     93.5352</x:v>
+        <x:v>    208.9602</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1449,7 +2649,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    122.5300</x:v>
+        <x:v>    268.6428</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1464,7 +2664,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     56.7240</x:v>
+        <x:v>    153.8658</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1479,7 +2679,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     59.3826</x:v>
+        <x:v>    157.6530</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1494,7 +2694,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     81.5944</x:v>
+        <x:v>    196.9025</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1509,7 +2709,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     74.3048</x:v>
+        <x:v>    183.2200</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1524,7 +2724,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    103.0344</x:v>
+        <x:v>    238.0025</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1539,7 +2739,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    259.2086</x:v>
+        <x:v>    385.4905</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1554,7 +2754,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     72.5896</x:v>
+        <x:v>    180.1857</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1569,7 +2769,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     91.8856</x:v>
+        <x:v>    215.9636</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1584,7 +2784,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    312.2100</x:v>
+        <x:v>    439.1479</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1599,7 +2799,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     93.1720</x:v>
+        <x:v>    218.4048</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1614,7 +2814,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    396.4972</x:v>
+        <x:v>    528.9429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1629,7 +2829,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     82.4520</x:v>
+        <x:v>    198.6537</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1644,7 +2844,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     89.7416</x:v>
+        <x:v>    212.2394</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1659,7 +2859,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     66.5864</x:v>
+        <x:v>    170.6660</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1674,7 +2874,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    106.4648</x:v>
+        <x:v>    244.5015</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1689,7 +2889,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    102.0552</x:v>
+        <x:v>    235.4667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1704,7 +2904,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     55.0088</x:v>
+        <x:v>    150.1483</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1719,7 +2919,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     84.1672</x:v>
+        <x:v>    201.5266</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1734,7 +2934,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     63.5848</x:v>
+        <x:v>    164.8731</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1749,7 +2949,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     88.8840</x:v>
+        <x:v>    210.7572</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1764,7 +2964,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.8616</x:v>
+        <x:v>    137.0710</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1779,7 +2979,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     75.1624</x:v>
+        <x:v>    184.9389</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1794,7 +2994,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     61.8696</x:v>
+        <x:v>    161.8281</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1809,7 +3009,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    133.0444</x:v>
+        <x:v>    309.1844</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1824,7 +3024,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     61.4408</x:v>
+        <x:v>    161.6654</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1839,7 +3039,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     69.5880</x:v>
+        <x:v>    175.0546</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1854,7 +3054,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     67.0152</x:v>
+        <x:v>    171.0923</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1869,7 +3069,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     60.1544</x:v>
+        <x:v>    158.7884</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1884,7 +3084,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     77.7352</x:v>
+        <x:v>    189.4607</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1899,7 +3099,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     79.4504</x:v>
+        <x:v>    192.5865</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1914,7 +3114,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    168.4090</x:v>
+        <x:v>    331.4712</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1929,7 +3129,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     95.1594</x:v>
+        <x:v>    227.5889</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1944,7 +3144,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     83.3096</x:v>
+        <x:v>    199.6032</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1959,7 +3159,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    304.9030</x:v>
+        <x:v>    456.3774</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1974,7 +3174,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     63.5848</x:v>
+        <x:v>    164.9000</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1989,7 +3189,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     67.0152</x:v>
+        <x:v>    170.4144</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2004,7 +3204,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     70.8744</x:v>
+        <x:v>    178.2328</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2019,7 +3219,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     66.1576</x:v>
+        <x:v>    169.0076</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2034,7 +3234,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     97.7532</x:v>
+        <x:v>    229.3701</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2049,7 +3249,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     84.1672</x:v>
+        <x:v>    201.5911</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2064,7 +3264,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    121.8220</x:v>
+        <x:v>    263.8611</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2079,7 +3279,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     74.3048</x:v>
+        <x:v>    183.3814</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2094,7 +3294,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     90.5992</x:v>
+        <x:v>    213.7269</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2109,7 +3309,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     77.3064</x:v>
+        <x:v>    188.6685</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2124,7 +3324,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     88.4552</x:v>
+        <x:v>    209.3140</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2139,7 +3339,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    185.8366</x:v>
+        <x:v>    336.8301</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2154,7 +3354,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    289.3822</x:v>
+        <x:v>    442.7561</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2169,7 +3369,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    151.7584</x:v>
+        <x:v>    311.7346</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2184,7 +3384,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    181.0988</x:v>
+        <x:v>    336.5523</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2199,7 +3399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     77.7352</x:v>
+        <x:v>    189.4177</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2214,7 +3414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     93.6008</x:v>
+        <x:v>    219.2884</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2229,7 +3429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     72.5896</x:v>
+        <x:v>    180.3795</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2244,7 +3444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     75.5912</x:v>
+        <x:v>    185.6289</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2259,7 +3459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     66.1576</x:v>
+        <x:v>    168.9323</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2274,7 +3474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    105.1784</x:v>
+        <x:v>    242.5499</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2289,7 +3489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     98.2590</x:v>
+        <x:v>    216.4500</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2304,7 +3504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     63.1560</x:v>
+        <x:v>    163.8980</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2319,7 +3519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     66.5864</x:v>
+        <x:v>    170.1280</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2334,7 +3534,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     66.1576</x:v>
+        <x:v>    169.1044</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2349,7 +3549,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     83.3096</x:v>
+        <x:v>    199.5925</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2364,7 +3564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     70.0168</x:v>
+        <x:v>    175.9491</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2379,7 +3579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     82.0232</x:v>
+        <x:v>    197.2159</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2394,7 +3594,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     95.1664</x:v>
+        <x:v>    226.2571</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2409,7 +3609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    100.8904</x:v>
+        <x:v>    233.3207</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2424,7 +3624,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     83.7384</x:v>
+        <x:v>    202.2354</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2439,7 +3639,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     78.5928</x:v>
+        <x:v>    191.1474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2454,7 +3654,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     82.8808</x:v>
+        <x:v>    198.8057</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2469,7 +3669,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     76.0200</x:v>
+        <x:v>    186.8407</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2484,7 +3684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     94.4584</x:v>
+        <x:v>    220.8943</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2499,7 +3699,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    176.2394</x:v>
+        <x:v>    324.3389</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2514,7 +3714,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    148.1924</x:v>
+        <x:v>    304.9020</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2529,7 +3729,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    259.8046</x:v>
+        <x:v>    411.0002</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2544,7 +3744,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     53.7224</x:v>
+        <x:v>    148.0299</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2559,7 +3759,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.4360</x:v>
+        <x:v>    145.9438</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2574,7 +3774,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     59.2968</x:v>
+        <x:v>    158.1939</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2589,7 +3789,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     53.2936</x:v>
+        <x:v>    147.4206</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2604,7 +3804,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     61.4408</x:v>
+        <x:v>    161.2457</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2619,7 +3819,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     68.3016</x:v>
+        <x:v>    172.7695</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2634,7 +3834,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     77.7352</x:v>
+        <x:v>    189.4177</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2649,7 +3849,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     83.7384</x:v>
+        <x:v>    200.3847</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2664,7 +3864,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    158.3304</x:v>
+        <x:v>    296.0269</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2679,7 +3879,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    307.6534</x:v>
+        <x:v>    459.3720</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2694,7 +3894,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     81.1656</x:v>
+        <x:v>    195.6530</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2709,7 +3909,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    108.0444</x:v>
+        <x:v>    248.5765</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2724,7 +3924,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    301.0228</x:v>
+        <x:v>    453.7082</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2739,7 +3939,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     83.3096</x:v>
+        <x:v>    199.6355</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2754,7 +3954,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    242.5616</x:v>
+        <x:v>    396.3322</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2769,7 +3969,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     78.5928</x:v>
+        <x:v>    190.9806</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2784,7 +3984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     89.7416</x:v>
+        <x:v>    212.2986</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2799,7 +3999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    101.7480</x:v>
+        <x:v>    235.2010</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2814,7 +4014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    377.3334</x:v>
+        <x:v>    519.8186</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2829,7 +4029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     81.1656</x:v>
+        <x:v>    196.9927</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2844,7 +4044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     87.5976</x:v>
+        <x:v>    207.6489</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2859,7 +4059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     88.4552</x:v>
+        <x:v>    209.5131</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2874,7 +4074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     93.6008</x:v>
+        <x:v>    219.1270</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2889,7 +4089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    104.3208</x:v>
+        <x:v>    240.0994</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2904,7 +4104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    203.7736</x:v>
+        <x:v>    358.6924</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2919,7 +4119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    348.8786</x:v>
+        <x:v>    499.5801</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2934,7 +4134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     90.5992</x:v>
+        <x:v>    213.4902</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2949,7 +4149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     75.5912</x:v>
+        <x:v>    185.5320</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2964,7 +4164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     76.0200</x:v>
+        <x:v>    186.3888</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2979,7 +4179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     73.8760</x:v>
+        <x:v>    182.4816</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2994,7 +4194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     91.4568</x:v>
+        <x:v>    214.9616</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3009,7 +4209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    179.8684</x:v>
+        <x:v>    317.4839</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3024,7 +4224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    125.6532</x:v>
+        <x:v>    277.2474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3039,7 +4239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    491.3162</x:v>
+        <x:v>    629.4254</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3054,7 +4254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    342.4116</x:v>
+        <x:v>    489.7423</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3069,7 +4269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    120.5146</x:v>
+        <x:v>    270.6494</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3084,7 +4284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    139.2882</x:v>
+        <x:v>    293.9071</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3099,7 +4299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     78.5928</x:v>
+        <x:v>    190.9645</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3114,7 +4314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     99.4964</x:v>
+        <x:v>    228.7728</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3129,7 +4329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     59.2968</x:v>
+        <x:v>    157.3493</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3144,7 +4344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     81.1656</x:v>
+        <x:v>    195.7983</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3159,7 +4359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    247.9934</x:v>
+        <x:v>    407.9652</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3174,7 +4374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     63.5848</x:v>
+        <x:v>    164.5503</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3189,7 +4389,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     85.8824</x:v>
+        <x:v>    204.5286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3204,7 +4404,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     84.1672</x:v>
+        <x:v>    201.9301</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3219,7 +4419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     91.4568</x:v>
+        <x:v>    214.9885</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3234,7 +4434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    207.0088</x:v>
+        <x:v>    345.8731</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3249,7 +4449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    120.9154</x:v>
+        <x:v>    276.9748</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3264,7 +4464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    118.3356</x:v>
+        <x:v>    268.5575</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3279,7 +4479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    255.7538</x:v>
+        <x:v>    415.0289</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3294,7 +4494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    237.6462</x:v>
+        <x:v>    399.2838</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3309,7 +4509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    244.6460</x:v>
+        <x:v>    383.0476</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3324,7 +4524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    326.8908</x:v>
+        <x:v>    480.4318</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3339,7 +4539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    123.9660</x:v>
+        <x:v>    267.6499</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3354,7 +4554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     64.4424</x:v>
+        <x:v>    166.2746</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3369,7 +4569,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     78.5928</x:v>
+        <x:v>    191.0774</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3384,7 +4584,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     79.0216</x:v>
+        <x:v>    192.6120</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3399,7 +4599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     87.5976</x:v>
+        <x:v>    208.0686</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3414,7 +4614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     76.8776</x:v>
+        <x:v>    187.9033</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3429,7 +4629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     89.7416</x:v>
+        <x:v>    212.0188</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3444,7 +4644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     91.8856</x:v>
+        <x:v>    221.5125</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3459,7 +4659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    100.8904</x:v>
+        <x:v>    233.8371</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3474,7 +4674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    236.3002</x:v>
+        <x:v>    377.7074</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3489,7 +4689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     93.6008</x:v>
+        <x:v>    219.4122</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3504,7 +4704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    120.7658</x:v>
+        <x:v>    275.0064</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3519,7 +4719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    139.0020</x:v>
+        <x:v>    296.7666</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3534,7 +4734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     76.4488</x:v>
+        <x:v>    187.1326</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3549,7 +4749,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     72.5896</x:v>
+        <x:v>    180.2665</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3564,7 +4764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     67.0152</x:v>
+        <x:v>    170.5489</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3579,7 +4779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    110.3240</x:v>
+        <x:v>    252.5674</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3594,7 +4794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     70.8744</x:v>
+        <x:v>    177.2161</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3609,7 +4809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    122.9378</x:v>
+        <x:v>    273.6303</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3624,7 +4824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     82.8808</x:v>
+        <x:v>    199.0962</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3639,7 +4839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    111.0390</x:v>
+        <x:v>    255.3793</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3654,7 +4854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     68.3016</x:v>
+        <x:v>    172.8502</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3669,7 +4869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     85.0248</x:v>
+        <x:v>    203.0410</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3684,7 +4884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     77.3064</x:v>
+        <x:v>    188.6309</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3699,7 +4899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     99.0326</x:v>
+        <x:v>    232.4769</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3714,7 +4914,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     64.4424</x:v>
+        <x:v>    166.1078</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3729,7 +4929,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     68.3016</x:v>
+        <x:v>    173.1569</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3744,7 +4944,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     92.7432</x:v>
+        <x:v>    217.5265</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3759,7 +4959,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     91.4568</x:v>
+        <x:v>    215.9731</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3774,7 +4974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     58.0104</x:v>
+        <x:v>    155.2794</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3789,7 +4989,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     75.5912</x:v>
+        <x:v>    185.6343</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3804,7 +5004,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     70.8744</x:v>
+        <x:v>    177.1622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3819,7 +5019,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     84.5960</x:v>
+        <x:v>    202.0821</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3834,7 +5034,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    209.1668</x:v>
+        <x:v>    346.8340</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3849,7 +5049,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    222.3310</x:v>
+        <x:v>    371.0859</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3864,7 +5064,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    139.7100</x:v>
+        <x:v>    296.4084</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3879,7 +5079,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    108.0234</x:v>
+        <x:v>    252.5760</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3894,7 +5094,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     55.8664</x:v>
+        <x:v>    151.6197</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3909,7 +5109,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.7368</x:v>
+        <x:v>    194.8985</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3924,7 +5124,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    207.6818</x:v>
+        <x:v>    356.8765</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3939,7 +5139,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     93.6008</x:v>
+        <x:v>    219.5520</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3954,7 +5154,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     78.5928</x:v>
+        <x:v>    190.9967</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3969,7 +5169,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     89.3128</x:v>
+        <x:v>    210.8392</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3984,7 +5184,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     74.3048</x:v>
+        <x:v>    183.7903</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3999,7 +5199,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    188.2318</x:v>
+        <x:v>    350.1575</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4014,7 +5214,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    162.1266</x:v>
+        <x:v>    315.6558</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4029,7 +5229,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     56.2952</x:v>
+        <x:v>    152.4872</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4044,7 +5244,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     63.5848</x:v>
+        <x:v>    164.5826</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4059,7 +5259,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     60.1544</x:v>
+        <x:v>    158.6969</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4074,7 +5274,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.3080</x:v>
+        <x:v>    194.5636</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4089,7 +5289,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    158.9858</x:v>
+        <x:v>    278.9615</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4104,7 +5304,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     92.7432</x:v>
+        <x:v>    217.4781</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4119,7 +5319,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    136.8720</x:v>
+        <x:v>    284.6294</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4134,7 +5334,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    217.9800</x:v>
+        <x:v>    376.1078</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4149,7 +5349,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    289.3822</x:v>
+        <x:v>    443.0444</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4164,7 +5364,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     87.1688</x:v>
+        <x:v>    207.1419</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4179,7 +5379,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    111.1816</x:v>
+        <x:v>    254.1303</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4194,7 +5394,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    932.2020</x:v>
+        <x:v>   1044.8097</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4209,7 +5409,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     86.3112</x:v>
+        <x:v>    213.0266</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4224,7 +5424,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     83.5888</x:v>
+        <x:v>    201.3899</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4239,7 +5439,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.4264</x:v>
+        <x:v>     93.4744</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4254,7 +5454,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.7128</x:v>
+        <x:v>     96.0969</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4269,7 +5469,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     59.7256</x:v>
+        <x:v>    148.4129</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4284,7 +5484,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     84.5960</x:v>
+        <x:v>    205.4755</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4299,7 +5499,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     51.1496</x:v>
+        <x:v>    128.6640</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4314,7 +5514,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.1512</x:v>
+        <x:v>    135.2270</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4329,7 +5529,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.5736</x:v>
+        <x:v>    110.5387</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4344,7 +5544,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     53.7224</x:v>
+        <x:v>    134.3002</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4359,7 +5559,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     65.3000</x:v>
+        <x:v>    160.2327</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4374,7 +5574,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    108.1800</x:v>
+        <x:v>    260.9937</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4389,7 +5589,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     69.5880</x:v>
+        <x:v>    169.9204</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4404,7 +5604,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    108.4732</x:v>
+        <x:v>    255.2311</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4419,7 +5619,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    296.1178</x:v>
+        <x:v>    421.1092</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4434,7 +5634,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     48.1480</x:v>
+        <x:v>    122.8079</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4449,7 +5649,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.5291</x:v>
+        <x:v>    103.9675</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4464,7 +5664,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     65.3000</x:v>
+        <x:v>    160.5365</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4479,7 +5679,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     74.7336</x:v>
+        <x:v>    181.9050</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4494,7 +5694,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    272.3448</x:v>
+        <x:v>    415.5540</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4509,7 +5709,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     56.7240</x:v>
+        <x:v>    141.2078</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4524,7 +5724,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.4264</x:v>
+        <x:v>     93.4686</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4539,7 +5739,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.8616</x:v>
+        <x:v>    119.4320</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4554,7 +5754,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     57.1528</x:v>
+        <x:v>    142.9290</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4569,7 +5769,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    162.3252</x:v>
+        <x:v>    312.3892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4584,7 +5784,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     29.2808</x:v>
+        <x:v>     83.4171</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4599,7 +5799,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     43.0024</x:v>
+        <x:v>    111.7925</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4614,7 +5814,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.2664</x:v>
+        <x:v>     29.7897</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4629,7 +5829,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     21.4195</x:v>
+        <x:v>     58.2173</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4644,7 +5844,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     21.1336</x:v>
+        <x:v>     67.5328</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4659,7 +5859,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     25.8504</x:v>
+        <x:v>     76.2721</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4674,7 +5874,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.9960</x:v>
+        <x:v>     86.5573</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4689,7 +5889,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.4264</x:v>
+        <x:v>     93.5153</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4704,7 +5904,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.2888</x:v>
+        <x:v>    114.1170</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4719,7 +5919,22 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    314.8738</x:v>
+        <x:v>    429.2956</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.3334</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4734,7 +5949,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.9816</x:v>
+        <x:v>     28.3276</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4749,7 +5964,67 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.2760</x:v>
+        <x:v>     65.6911</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.9122</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.0440</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.0440</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.0965</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4764,7 +6039,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.4088</x:v>
+        <x:v>     21.5644</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4779,7 +6054,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.6952</x:v>
+        <x:v>     32.8306</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4794,7 +6069,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.4120</x:v>
+        <x:v>     41.3595</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4809,7 +6084,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.8376</x:v>
+        <x:v>     31.3043</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4824,7 +6099,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.5560</x:v>
+        <x:v>     45.3797</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4839,7 +6114,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     22.8488</x:v>
+        <x:v>     70.4043</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4854,7 +6129,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     15.9880</x:v>
+        <x:v>     57.2826</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4869,7 +6144,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.7000</x:v>
+        <x:v>     49.3883</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4884,7 +6159,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.9960</x:v>
+        <x:v>     86.5398</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4899,7 +6174,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     97.4600</x:v>
+        <x:v>    235.5922</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4914,7 +6189,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.8392</x:v>
+        <x:v>     28.2984</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4929,7 +6204,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1256</x:v>
+        <x:v>     39.0351</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4944,7 +6219,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     24.1352</x:v>
+        <x:v>     73.5291</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4959,7 +6234,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.8440</x:v>
+        <x:v>     53.7648</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4974,7 +6249,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.6968</x:v>
+        <x:v>     38.3829</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4989,7 +6264,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     16.8456</x:v>
+        <x:v>     58.8615</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5004,7 +6279,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     16.8456</x:v>
+        <x:v>     58.8615</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5019,7 +6294,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.7000</x:v>
+        <x:v>     21.8390</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5034,7 +6309,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.4152</x:v>
+        <x:v>     52.4058</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5049,7 +6324,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     18.9896</x:v>
+        <x:v>     63.1504</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5064,7 +6339,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     24.9928</x:v>
+        <x:v>     74.6874</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5079,7 +6354,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     48.1480</x:v>
+        <x:v>    122.5626</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5094,7 +6369,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     19.4184</x:v>
+        <x:v>     63.7617</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5109,7 +6384,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     16.8456</x:v>
+        <x:v>     58.8732</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5124,7 +6399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     19.4184</x:v>
+        <x:v>     63.7734</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5139,7 +6414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.4248</x:v>
+        <x:v>     87.4197</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5154,7 +6429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.2792</x:v>
+        <x:v>     77.1404</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5169,7 +6444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     24.9928</x:v>
+        <x:v>     74.6348</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5184,7 +6459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     22.4200</x:v>
+        <x:v>     69.5535</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5199,7 +6474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.9944</x:v>
+        <x:v>     80.5318</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5214,7 +6489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.5688</x:v>
+        <x:v>     91.6736</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5229,7 +6504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.8616</x:v>
+        <x:v>    119.4787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5244,7 +6519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    120.9224</x:v>
+        <x:v>    280.8947</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5259,7 +6534,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     18.9896</x:v>
+        <x:v>     62.9460</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5274,7 +6549,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.1384</x:v>
+        <x:v>     84.8148</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5289,7 +6564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.9960</x:v>
+        <x:v>     86.6800</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5304,7 +6579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.2888</x:v>
+        <x:v>    114.0119</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5319,7 +6594,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     48.5768</x:v>
+        <x:v>    123.1271</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5334,7 +6609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     18.1320</x:v>
+        <x:v>     61.3087</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5349,7 +6624,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     29.7096</x:v>
+        <x:v>     83.9991</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5364,7 +6639,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.5752</x:v>
+        <x:v>    116.8095</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5379,7 +6654,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     56.2952</x:v>
+        <x:v>    140.1467</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5394,7 +6669,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.5720</x:v>
+        <x:v>    104.0108</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5409,7 +6684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     58.8680</x:v>
+        <x:v>    146.3311</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5424,7 +6699,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     43.0024</x:v>
+        <x:v>    111.1850</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5439,7 +6714,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     70.8744</x:v>
+        <x:v>    173.9487</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5454,7 +6729,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     43.8600</x:v>
+        <x:v>    113.5408</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5469,7 +6744,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.8552</x:v>
+        <x:v>     94.6698</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5484,7 +6759,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.9944</x:v>
+        <x:v>     80.5843</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5499,7 +6774,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.7048</x:v>
+        <x:v>     66.4191</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5514,7 +6789,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.2792</x:v>
+        <x:v>     77.5610</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5529,7 +6804,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     14.2728</x:v>
+        <x:v>     54.0314</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5544,7 +6819,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.8408</x:v>
+        <x:v>     42.1286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5559,7 +6834,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     18.5608</x:v>
+        <x:v>     62.1536</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5574,7 +6849,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     16.8456</x:v>
+        <x:v>     58.8966</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5589,7 +6864,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     14.2728</x:v>
+        <x:v>     54.1249</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5604,7 +6879,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.2712</x:v>
+        <x:v>     48.7186</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5619,7 +6894,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     15.9880</x:v>
+        <x:v>     57.2826</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5634,7 +6909,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.5656</x:v>
+        <x:v>     80.5163</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5649,7 +6924,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.7048</x:v>
+        <x:v>     66.4483</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5664,7 +6939,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     40.4296</x:v>
+        <x:v>    107.1727</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5679,7 +6954,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.7000</x:v>
+        <x:v>     49.2189</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5694,7 +6969,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.2712</x:v>
+        <x:v>     48.4148</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5709,7 +6984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.2712</x:v>
+        <x:v>     48.4207</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5724,7 +6999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.1283</x:v>
+        <x:v>     48.1507</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5739,7 +7014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     14.2728</x:v>
+        <x:v>     54.0548</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5754,7 +7029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.2712</x:v>
+        <x:v>     48.5609</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5769,7 +7044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     15.5592</x:v>
+        <x:v>     56.4611</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5784,7 +7059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     16.8456</x:v>
+        <x:v>     58.8732</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5799,7 +7074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     18.9896</x:v>
+        <x:v>     62.9401</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5814,7 +7089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     21.1336</x:v>
+        <x:v>     67.0596</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5829,7 +7104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.2792</x:v>
+        <x:v>     77.2105</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5844,7 +7119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.9976</x:v>
+        <x:v>     92.5594</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5859,7 +7134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.1416</x:v>
+        <x:v>     96.9126</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5874,7 +7149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.5736</x:v>
+        <x:v>    110.3518</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5889,7 +7164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     66.5864</x:v>
+        <x:v>    163.2524</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5904,7 +7179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     94.8872</x:v>
+        <x:v>    229.2158</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5919,7 +7194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     40.4296</x:v>
+        <x:v>    105.7824</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5934,7 +7209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.7160</x:v>
+        <x:v>    108.4574</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5949,7 +7224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0040</x:v>
+        <x:v>    117.5785</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5964,7 +7239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.2888</x:v>
+        <x:v>    113.8833</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5979,7 +7254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.4328</x:v>
+        <x:v>    118.5111</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5994,7 +7269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     51.1496</x:v>
+        <x:v>    128.7341</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6009,7 +7284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.8648</x:v>
+        <x:v>    132.4351</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6024,7 +7299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     55.8664</x:v>
+        <x:v>    139.1265</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6039,7 +7314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.1464</x:v>
+        <x:v>    115.8010</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6054,7 +7329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.7160</x:v>
+        <x:v>    108.4633</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6069,7 +7344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.5736</x:v>
+        <x:v>    110.2524</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6084,7 +7359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.4360</x:v>
+        <x:v>    131.3507</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6099,7 +7374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     72.5896</x:v>
+        <x:v>    177.0149</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6114,7 +7389,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     89.7416</x:v>
+        <x:v>    217.1172</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6129,7 +7404,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.3080</x:v>
+        <x:v>    195.0208</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6144,7 +7419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    159.3166</x:v>
+        <x:v>    307.0345</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6159,7 +7434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     69.1592</x:v>
+        <x:v>    169.0171</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6174,7 +7449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     43.0024</x:v>
+        <x:v>    111.4187</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6189,7 +7464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     57.5816</x:v>
+        <x:v>    142.6991</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6204,7 +7479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     64.4424</x:v>
+        <x:v>    158.2099</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6219,7 +7494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    301.8558</x:v>
+        <x:v>    436.1354</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6234,7 +7509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.9992</x:v>
+        <x:v>     98.6784</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6249,7 +7524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.7080</x:v>
+        <x:v>     77.9386</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6264,7 +7539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.1368</x:v>
+        <x:v>     78.7835</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6279,7 +7554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.4232</x:v>
+        <x:v>     81.3417</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6294,7 +7569,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.5688</x:v>
+        <x:v>     91.6794</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6309,7 +7584,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.9976</x:v>
+        <x:v>     92.5535</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6324,7 +7599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.2856</x:v>
+        <x:v>    101.3242</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6339,7 +7614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     40.4296</x:v>
+        <x:v>    105.7766</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6354,7 +7629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8632</x:v>
+        <x:v>    125.8371</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6369,7 +7644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     61.4408</x:v>
+        <x:v>    151.3257</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6384,7 +7659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     90.1704</x:v>
+        <x:v>    218.1854</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6399,7 +7674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    265.9128</x:v>
+        <x:v>    403.1011</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6414,7 +7689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     56.2952</x:v>
+        <x:v>    139.8371</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6429,7 +7704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     82.2884</x:v>
+        <x:v>    201.8574</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6444,7 +7719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.5736</x:v>
+        <x:v>    110.2524</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6459,7 +7734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     64.4424</x:v>
+        <x:v>    158.6129</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6474,7 +7749,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     43.0024</x:v>
+        <x:v>    111.1558</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6489,7 +7764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.4360</x:v>
+        <x:v>    131.5259</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6504,7 +7779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.2888</x:v>
+        <x:v>    113.8717</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6519,7 +7794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.1512</x:v>
+        <x:v>    135.4022</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6534,7 +7809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.4344</x:v>
+        <x:v>    125.1032</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6549,7 +7824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     75.5912</x:v>
+        <x:v>    185.2960</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6564,7 +7839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.9992</x:v>
+        <x:v>     98.6725</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6579,7 +7854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.9992</x:v>
+        <x:v>     98.6725</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6594,7 +7869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4280</x:v>
+        <x:v>     99.5584</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6609,7 +7884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4280</x:v>
+        <x:v>     99.5525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6624,7 +7899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.2872</x:v>
+        <x:v>    107.5833</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6639,7 +7914,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.1464</x:v>
+        <x:v>    115.6842</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6654,7 +7929,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     53.7224</x:v>
+        <x:v>    134.2418</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6669,7 +7944,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     72.4330</x:v>
+        <x:v>    177.6644</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6684,7 +7959,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     74.7336</x:v>
+        <x:v>    182.2131</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6699,7 +7974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.1448</x:v>
+        <x:v>    109.3549</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6714,7 +7989,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.4360</x:v>
+        <x:v>    131.9348</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6729,7 +8004,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.8632</x:v>
+        <x:v>    125.8138</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6744,7 +8019,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     66.1576</x:v>
+        <x:v>    162.1329</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6759,7 +8034,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     64.8712</x:v>
+        <x:v>    159.1366</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6774,7 +8049,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     75.1624</x:v>
+        <x:v>    182.8901</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6789,7 +8064,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     75.1624</x:v>
+        <x:v>    182.8901</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6804,7 +8079,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     58.8680</x:v>
+        <x:v>    145.5726</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6819,7 +8094,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     81.5944</x:v>
+        <x:v>    197.9657</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6834,7 +8109,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    417.6344</x:v>
+        <x:v>    546.4461</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6849,7 +8124,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     61.8696</x:v>
+        <x:v>    152.3108</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6864,7 +8139,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     79.8792</x:v>
+        <x:v>    194.0918</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6879,7 +8154,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     55.8664</x:v>
+        <x:v>    140.3699</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6894,7 +8169,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     53.7224</x:v>
+        <x:v>    134.2126</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6909,7 +8184,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     62.7272</x:v>
+        <x:v>    154.3161</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6924,7 +8199,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     63.1560</x:v>
+        <x:v>    155.2312</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6939,7 +8214,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     62.7272</x:v>
+        <x:v>    154.2343</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6954,7 +8229,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     95.3160</x:v>
+        <x:v>    230.1598</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6969,7 +8244,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     74.3048</x:v>
+        <x:v>    180.9320</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6984,7 +8259,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    132.3022</x:v>
+        <x:v>    243.3895</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6999,7 +8274,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     76.8776</x:v>
+        <x:v>    187.0297</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7014,7 +8289,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    142.3318</x:v>
+        <x:v>    295.5251</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7029,7 +8304,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    476.9252</x:v>
+        <x:v>    615.6501</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7044,7 +8319,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     57.1528</x:v>
+        <x:v>    141.7139</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7059,7 +8334,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     60.5832</x:v>
+        <x:v>    149.4898</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7074,7 +8349,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    110.3844</x:v>
+        <x:v>    206.7251</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7089,7 +8364,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     61.0120</x:v>
+        <x:v>    150.9646</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7104,7 +8379,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     60.1544</x:v>
+        <x:v>    149.0236</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7119,7 +8394,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     55.4376</x:v>
+        <x:v>    137.9720</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7134,7 +8409,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     73.8760</x:v>
+        <x:v>    179.9060</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7149,7 +8424,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     79.8792</x:v>
+        <x:v>    194.0511</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7164,7 +8439,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     71.3032</x:v>
+        <x:v>    173.8901</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7179,7 +8454,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     86.3112</x:v>
+        <x:v>    208.9775</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7194,7 +8469,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    145.7272</x:v>
+        <x:v>    313.7100</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7209,7 +8484,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    802.8620</x:v>
+        <x:v>    917.9638</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7224,7 +8499,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    136.2376</x:v>
+        <x:v>    307.1660</x:v>
       </x:c>
     </x:row>
     <x:row>
